--- a/database/event/5226/event_5226_evp_summary.xlsx
+++ b/database/event/5226/event_5226_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>5.7307</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7433</v>
+        <v>3.6633</v>
       </c>
       <c r="E2" t="n">
         <v>10.3092</v>
@@ -514,7 +514,7 @@
         <v>3.8457</v>
       </c>
       <c r="H2" t="n">
-        <v>8.305199999999999</v>
+        <v>8.2126</v>
       </c>
       <c r="I2" t="n">
         <v>8.4217</v>
@@ -548,7 +548,7 @@
         <v>5.3266</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4497</v>
+        <v>3.3737</v>
       </c>
       <c r="E3" t="n">
         <v>9.5823</v>
@@ -560,7 +560,7 @@
         <v>3.1188</v>
       </c>
       <c r="H3" t="n">
-        <v>8.056800000000001</v>
+        <v>7.967</v>
       </c>
       <c r="I3" t="n">
         <v>8.1698</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.9965</v>
+        <v>7.9472</v>
       </c>
       <c r="C4" t="n">
-        <v>4.4451</v>
+        <v>4.4177</v>
       </c>
       <c r="D4" t="n">
-        <v>2.809</v>
+        <v>2.7223</v>
       </c>
       <c r="E4" t="n">
-        <v>7.9965</v>
+        <v>7.9472</v>
       </c>
       <c r="F4" t="n">
-        <v>5.894</v>
+        <v>5.8447</v>
       </c>
       <c r="G4" t="n">
         <v>2.1025</v>
       </c>
       <c r="H4" t="n">
-        <v>6.9387</v>
+        <v>6.8614</v>
       </c>
       <c r="I4" t="n">
         <v>7.0361</v>
@@ -640,7 +640,7 @@
         <v>4.0749</v>
       </c>
       <c r="D5" t="n">
-        <v>2.54</v>
+        <v>2.4766</v>
       </c>
       <c r="E5" t="n">
         <v>7.3305</v>
@@ -686,7 +686,7 @@
         <v>3.6191</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2088</v>
+        <v>2.1499</v>
       </c>
       <c r="E6" t="n">
         <v>6.5106</v>
@@ -732,7 +732,7 @@
         <v>3.593</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E7" t="n">
         <v>6.4635</v>
@@ -778,7 +778,7 @@
         <v>3.593</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E8" t="n">
         <v>6.4635</v>
@@ -824,7 +824,7 @@
         <v>3.593</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E9" t="n">
         <v>6.4635</v>
@@ -870,7 +870,7 @@
         <v>3.4385</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0775</v>
+        <v>2.0205</v>
       </c>
       <c r="E10" t="n">
         <v>6.1857</v>
@@ -916,7 +916,7 @@
         <v>3.3102</v>
       </c>
       <c r="D11" t="n">
-        <v>1.9842</v>
+        <v>1.9285</v>
       </c>
       <c r="E11" t="n">
         <v>5.9548</v>
@@ -962,7 +962,7 @@
         <v>3.2602</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9479</v>
+        <v>1.8927</v>
       </c>
       <c r="E12" t="n">
         <v>5.8649</v>
@@ -1008,7 +1008,7 @@
         <v>3.1456</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8647</v>
+        <v>1.8106</v>
       </c>
       <c r="E13" t="n">
         <v>5.6588</v>
@@ -1054,7 +1054,7 @@
         <v>2.9293</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7074</v>
+        <v>1.6555</v>
       </c>
       <c r="E14" t="n">
         <v>5.2696</v>
@@ -1100,7 +1100,7 @@
         <v>2.9272</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7059</v>
+        <v>1.654</v>
       </c>
       <c r="E15" t="n">
         <v>5.2658</v>
@@ -1146,7 +1146,7 @@
         <v>2.7643</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5875</v>
+        <v>1.5373</v>
       </c>
       <c r="E16" t="n">
         <v>4.9728</v>
@@ -1192,7 +1192,7 @@
         <v>2.76</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5844</v>
+        <v>1.5342</v>
       </c>
       <c r="E17" t="n">
         <v>4.9651</v>
@@ -1238,7 +1238,7 @@
         <v>2.5954</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4648</v>
+        <v>1.4162</v>
       </c>
       <c r="E18" t="n">
         <v>4.669</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.6075</v>
+        <v>4.5649</v>
       </c>
       <c r="C19" t="n">
-        <v>2.5612</v>
+        <v>2.5376</v>
       </c>
       <c r="D19" t="n">
-        <v>1.44</v>
+        <v>1.3747</v>
       </c>
       <c r="E19" t="n">
-        <v>4.6075</v>
+        <v>4.5649</v>
       </c>
       <c r="F19" t="n">
-        <v>3.8144</v>
+        <v>3.7718</v>
       </c>
       <c r="G19" t="n">
         <v>0.7931</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8144</v>
+        <v>3.7718</v>
       </c>
       <c r="I19" t="n">
         <v>3.8679</v>
@@ -1330,7 +1330,7 @@
         <v>2.4534</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3616</v>
+        <v>1.3144</v>
       </c>
       <c r="E20" t="n">
         <v>4.4135</v>
@@ -1376,7 +1376,7 @@
         <v>2.4372</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3498</v>
+        <v>1.3028</v>
       </c>
       <c r="E21" t="n">
         <v>4.3844</v>
@@ -1422,7 +1422,7 @@
         <v>2.3688</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3001</v>
+        <v>1.2538</v>
       </c>
       <c r="E22" t="n">
         <v>4.2613</v>
@@ -1468,7 +1468,7 @@
         <v>2.3256</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2687</v>
+        <v>1.2228</v>
       </c>
       <c r="E23" t="n">
         <v>4.1836</v>
@@ -1514,7 +1514,7 @@
         <v>2.308</v>
       </c>
       <c r="D24" t="n">
-        <v>1.256</v>
+        <v>1.2102</v>
       </c>
       <c r="E24" t="n">
         <v>4.152</v>
@@ -1560,7 +1560,7 @@
         <v>2.1764</v>
       </c>
       <c r="D25" t="n">
-        <v>1.1603</v>
+        <v>1.1159</v>
       </c>
       <c r="E25" t="n">
         <v>3.9153</v>
@@ -1606,7 +1606,7 @@
         <v>2.0116</v>
       </c>
       <c r="D26" t="n">
-        <v>1.0405</v>
+        <v>0.9978</v>
       </c>
       <c r="E26" t="n">
         <v>3.6187</v>
@@ -1652,7 +1652,7 @@
         <v>1.9917</v>
       </c>
       <c r="D27" t="n">
-        <v>1.0261</v>
+        <v>0.9836</v>
       </c>
       <c r="E27" t="n">
         <v>3.583</v>
@@ -1698,7 +1698,7 @@
         <v>1.9678</v>
       </c>
       <c r="D28" t="n">
-        <v>1.0087</v>
+        <v>0.9664</v>
       </c>
       <c r="E28" t="n">
         <v>3.5399</v>
@@ -1744,7 +1744,7 @@
         <v>1.8902</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9523</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="E29" t="n">
         <v>3.4004</v>
@@ -1790,7 +1790,7 @@
         <v>1.8748</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9411</v>
+        <v>0.8998</v>
       </c>
       <c r="E30" t="n">
         <v>3.3727</v>
@@ -1836,7 +1836,7 @@
         <v>1.8529</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9252</v>
+        <v>0.884</v>
       </c>
       <c r="E31" t="n">
         <v>3.3332</v>
@@ -1882,7 +1882,7 @@
         <v>1.8385</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9147</v>
+        <v>0.8737</v>
       </c>
       <c r="E32" t="n">
         <v>3.3073</v>
@@ -1928,7 +1928,7 @@
         <v>1.8053</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="E33" t="n">
         <v>3.2477</v>
@@ -1974,7 +1974,7 @@
         <v>1.7597</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8575</v>
+        <v>0.8173</v>
       </c>
       <c r="E34" t="n">
         <v>3.1656</v>
@@ -2020,7 +2020,7 @@
         <v>1.7002</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8142</v>
+        <v>0.7746</v>
       </c>
       <c r="E35" t="n">
         <v>3.0585</v>
@@ -2066,7 +2066,7 @@
         <v>1.66</v>
       </c>
       <c r="D36" t="n">
-        <v>0.785</v>
+        <v>0.7458</v>
       </c>
       <c r="E36" t="n">
         <v>2.9862</v>
@@ -2112,7 +2112,7 @@
         <v>1.6586</v>
       </c>
       <c r="D37" t="n">
-        <v>0.784</v>
+        <v>0.7448</v>
       </c>
       <c r="E37" t="n">
         <v>2.9837</v>
@@ -2158,7 +2158,7 @@
         <v>1.495</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6651</v>
+        <v>0.6276</v>
       </c>
       <c r="E38" t="n">
         <v>2.6895</v>
@@ -2204,7 +2204,7 @@
         <v>1.3576</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5653</v>
+        <v>0.5291</v>
       </c>
       <c r="E39" t="n">
         <v>2.4423</v>
@@ -2250,7 +2250,7 @@
         <v>1.3038</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5261</v>
+        <v>0.4905</v>
       </c>
       <c r="E40" t="n">
         <v>2.3454</v>
@@ -2296,7 +2296,7 @@
         <v>1.196</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4478</v>
+        <v>0.4132</v>
       </c>
       <c r="E41" t="n">
         <v>2.1515</v>
@@ -2342,7 +2342,7 @@
         <v>1.0179</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3184</v>
+        <v>0.2856</v>
       </c>
       <c r="E42" t="n">
         <v>1.8311</v>
@@ -2388,7 +2388,7 @@
         <v>0.9959</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3024</v>
+        <v>0.2698</v>
       </c>
       <c r="E43" t="n">
         <v>1.7915</v>
@@ -2434,7 +2434,7 @@
         <v>0.865</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2073</v>
+        <v>0.176</v>
       </c>
       <c r="E44" t="n">
         <v>1.5561</v>
@@ -2480,7 +2480,7 @@
         <v>0.8584000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2025</v>
+        <v>0.1713</v>
       </c>
       <c r="E45" t="n">
         <v>1.5442</v>
@@ -2526,7 +2526,7 @@
         <v>0.8313</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1828</v>
+        <v>0.1519</v>
       </c>
       <c r="E46" t="n">
         <v>1.4955</v>
@@ -2572,7 +2572,7 @@
         <v>0.78</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1455</v>
+        <v>0.1151</v>
       </c>
       <c r="E47" t="n">
         <v>1.4032</v>
@@ -2618,7 +2618,7 @@
         <v>0.7681</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1369</v>
+        <v>0.1066</v>
       </c>
       <c r="E48" t="n">
         <v>1.3818</v>
@@ -2664,7 +2664,7 @@
         <v>0.7633</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1333</v>
+        <v>0.1031</v>
       </c>
       <c r="E49" t="n">
         <v>1.3731</v>
@@ -2710,7 +2710,7 @@
         <v>0.71</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0946</v>
+        <v>0.0649</v>
       </c>
       <c r="E50" t="n">
         <v>1.2772</v>
@@ -2756,7 +2756,7 @@
         <v>0.6708</v>
       </c>
       <c r="D51" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="E51" t="n">
         <v>1.2067</v>
@@ -2802,7 +2802,7 @@
         <v>0.6355</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0405</v>
+        <v>0.0116</v>
       </c>
       <c r="E52" t="n">
         <v>1.1433</v>
@@ -2848,7 +2848,7 @@
         <v>0.5934</v>
       </c>
       <c r="D53" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0186</v>
       </c>
       <c r="E53" t="n">
         <v>1.0675</v>
@@ -2894,7 +2894,7 @@
         <v>0.5891</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0068</v>
+        <v>-0.0217</v>
       </c>
       <c r="E54" t="n">
         <v>1.0598</v>
@@ -2940,7 +2940,7 @@
         <v>0.5578</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.016</v>
+        <v>-0.0442</v>
       </c>
       <c r="E55" t="n">
         <v>1.0034</v>
@@ -2986,7 +2986,7 @@
         <v>0.5447</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.0255</v>
+        <v>-0.0536</v>
       </c>
       <c r="E56" t="n">
         <v>0.9798</v>
@@ -3032,7 +3032,7 @@
         <v>0.4757</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.0756</v>
+        <v>-0.103</v>
       </c>
       <c r="E57" t="n">
         <v>0.8558</v>
@@ -3078,7 +3078,7 @@
         <v>0.3891</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.1386</v>
+        <v>-0.1651</v>
       </c>
       <c r="E58" t="n">
         <v>0.6999</v>
@@ -3124,7 +3124,7 @@
         <v>0.3275</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.1834</v>
+        <v>-0.2092</v>
       </c>
       <c r="E59" t="n">
         <v>0.5891</v>
@@ -3170,7 +3170,7 @@
         <v>0.2942</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.2075</v>
+        <v>-0.233</v>
       </c>
       <c r="E60" t="n">
         <v>0.5293</v>
@@ -3216,7 +3216,7 @@
         <v>0.2336</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.2516</v>
+        <v>-0.2765</v>
       </c>
       <c r="E61" t="n">
         <v>0.4203</v>
@@ -3262,7 +3262,7 @@
         <v>-0.0309</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.4438</v>
+        <v>-0.466</v>
       </c>
       <c r="E62" t="n">
         <v>-0.0555</v>
@@ -3308,7 +3308,7 @@
         <v>-0.0476</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.456</v>
+        <v>-0.4781</v>
       </c>
       <c r="E63" t="n">
         <v>-0.0857</v>
@@ -3354,7 +3354,7 @@
         <v>-0.1815</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.5533</v>
+        <v>-0.574</v>
       </c>
       <c r="E64" t="n">
         <v>-0.3265</v>
@@ -3400,7 +3400,7 @@
         <v>-0.2165</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.5787</v>
+        <v>-0.599</v>
       </c>
       <c r="E65" t="n">
         <v>-0.3894</v>
@@ -3446,7 +3446,7 @@
         <v>-0.2311</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.5893</v>
+        <v>-0.6096</v>
       </c>
       <c r="E66" t="n">
         <v>-0.4158</v>
@@ -3492,7 +3492,7 @@
         <v>-0.2748</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.621</v>
+        <v>-0.6408</v>
       </c>
       <c r="E67" t="n">
         <v>-0.4943</v>
@@ -3538,7 +3538,7 @@
         <v>-0.3103</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.6469</v>
+        <v>-0.6663</v>
       </c>
       <c r="E68" t="n">
         <v>-0.5582</v>
@@ -3584,7 +3584,7 @@
         <v>-0.3399</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.6684</v>
+        <v>-0.6875</v>
       </c>
       <c r="E69" t="n">
         <v>-0.6115</v>
@@ -3630,7 +3630,7 @@
         <v>-0.3402</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.6686</v>
+        <v>-0.6877</v>
       </c>
       <c r="E70" t="n">
         <v>-0.612</v>
@@ -3676,7 +3676,7 @@
         <v>-0.3672</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.6882</v>
+        <v>-0.7071</v>
       </c>
       <c r="E71" t="n">
         <v>-0.6605</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5119</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.7934</v>
+        <v>-0.8108</v>
       </c>
       <c r="E72" t="n">
         <v>-0.9209000000000001</v>
@@ -3768,7 +3768,7 @@
         <v>-0.7113</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9383</v>
+        <v>-0.9537</v>
       </c>
       <c r="E73" t="n">
         <v>-1.2795</v>
@@ -3814,7 +3814,7 @@
         <v>-0.9737</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.129</v>
+        <v>-1.1418</v>
       </c>
       <c r="E74" t="n">
         <v>-1.7517</v>
@@ -3850,93 +3850,93 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.9232</v>
+        <v>-1.9177</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.0691</v>
+        <v>-1.066</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1983</v>
+        <v>-1.2079</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.9232</v>
+        <v>-1.9177</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.9232</v>
+        <v>-0.9177</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.9232</v>
+        <v>-0.9177</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.9232</v>
+        <v>-0.9411</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K75" t="n">
-        <v>293</v>
+        <v>748</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.9232</v>
+        <v>-1.9411</v>
       </c>
       <c r="N75" t="n">
-        <v>293</v>
+        <v>870</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.9281</v>
+        <v>-1.9232</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.0718</v>
+        <v>-1.0691</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2003</v>
+        <v>-1.2101</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.9281</v>
+        <v>-1.9232</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.9281</v>
+        <v>-1.9232</v>
       </c>
       <c r="G76" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.9281</v>
+        <v>-1.9232</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9411</v>
+        <v>-1.9232</v>
       </c>
       <c r="J76" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>748</v>
+        <v>293</v>
       </c>
       <c r="L76" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.9411</v>
+        <v>-1.9232</v>
       </c>
       <c r="N76" t="n">
-        <v>870</v>
+        <v>293</v>
       </c>
     </row>
     <row r="77">
@@ -3952,7 +3952,7 @@
         <v>-1.1466</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2546</v>
+        <v>-1.2657</v>
       </c>
       <c r="E77" t="n">
         <v>-2.0627</v>
@@ -3998,7 +3998,7 @@
         <v>-1.3016</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3673</v>
+        <v>-1.3768</v>
       </c>
       <c r="E78" t="n">
         <v>-2.3415</v>
@@ -4044,7 +4044,7 @@
         <v>-1.3208</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3812</v>
+        <v>-1.3905</v>
       </c>
       <c r="E79" t="n">
         <v>-2.376</v>
@@ -4090,7 +4090,7 @@
         <v>-1.5011</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5122</v>
+        <v>-1.5197</v>
       </c>
       <c r="E80" t="n">
         <v>-2.7003</v>
@@ -4136,7 +4136,7 @@
         <v>-1.5566</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5526</v>
+        <v>-1.5596</v>
       </c>
       <c r="E81" t="n">
         <v>-2.8003</v>
@@ -4182,7 +4182,7 @@
         <v>-1.6155</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.5954</v>
+        <v>-1.6017</v>
       </c>
       <c r="E82" t="n">
         <v>-2.9062</v>
@@ -4228,7 +4228,7 @@
         <v>-1.7122</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.6657</v>
+        <v>-1.6711</v>
       </c>
       <c r="E83" t="n">
         <v>-3.0802</v>
@@ -4274,7 +4274,7 @@
         <v>-1.7734</v>
       </c>
       <c r="D84" t="n">
-        <v>-1.7101</v>
+        <v>-1.7149</v>
       </c>
       <c r="E84" t="n">
         <v>-3.1902</v>
@@ -4320,7 +4320,7 @@
         <v>-1.8225</v>
       </c>
       <c r="D85" t="n">
-        <v>-1.7458</v>
+        <v>-1.7501</v>
       </c>
       <c r="E85" t="n">
         <v>-3.2785</v>
@@ -4366,7 +4366,7 @@
         <v>-1.9877</v>
       </c>
       <c r="D86" t="n">
-        <v>-1.8659</v>
+        <v>-1.8685</v>
       </c>
       <c r="E86" t="n">
         <v>-3.5757</v>
@@ -4412,7 +4412,7 @@
         <v>-2.2056</v>
       </c>
       <c r="D87" t="n">
-        <v>-2.0243</v>
+        <v>-2.0247</v>
       </c>
       <c r="E87" t="n">
         <v>-3.9678</v>
@@ -4458,7 +4458,7 @@
         <v>-2.5353</v>
       </c>
       <c r="D88" t="n">
-        <v>-2.2638</v>
+        <v>-2.2609</v>
       </c>
       <c r="E88" t="n">
         <v>-4.5608</v>
@@ -4504,7 +4504,7 @@
         <v>-2.841</v>
       </c>
       <c r="D89" t="n">
-        <v>-2.486</v>
+        <v>-2.48</v>
       </c>
       <c r="E89" t="n">
         <v>-5.1107</v>
@@ -4550,7 +4550,7 @@
         <v>-2.8771</v>
       </c>
       <c r="D90" t="n">
-        <v>-2.5123</v>
+        <v>-2.5059</v>
       </c>
       <c r="E90" t="n">
         <v>-5.1758</v>
@@ -4596,7 +4596,7 @@
         <v>-3.1192</v>
       </c>
       <c r="D91" t="n">
-        <v>-2.6882</v>
+        <v>-2.6795</v>
       </c>
       <c r="E91" t="n">
         <v>-5.6113</v>
